--- a/aq_files/0080.xlsx
+++ b/aq_files/0080.xlsx
@@ -1,101 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>Q.No,Question,Type,Difficulty</t>
-  </si>
-  <si>
-    <t>1,What is Retrieval-Augmented Generation (RAG)? Explain the core concept.,Theory,Easy</t>
-  </si>
-  <si>
-    <t>2,What are the components of a RAG system? Explain retriever, generator, and knowledge base.,Technical,Medium</t>
-  </si>
-  <si>
-    <t>3,How does RAG improve upon standard LLM generation? What problems does it solve?,Theory,Medium</t>
-  </si>
-  <si>
-    <t>4,What is dense retrieval vs sparse retrieval? Compare approaches like BM25 and embedding-based retrieval.,Technical,Medium</t>
-  </si>
-  <si>
-    <t>5,What is a vector database? How do databases like Pinecone, Weaviate, and Chroma work?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>6,Explain the difference between naive RAG, advanced RAG, and modular RAG.,Theory,Medium</t>
-  </si>
-  <si>
-    <t>7,What is a workflow in AI systems? How does it differ from RAG and Agentic AI?,Theory,Easy</t>
-  </si>
-  <si>
-    <t>8,What is Agentic AI? How does it extend beyond traditional RAG and workflows?,Theory,Medium</t>
-  </si>
-  <si>
-    <t>9,What are the key capabilities of AI agents (planning, memory, tool use, reflection)?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>10,Explain the difference between single-agent and multi-agent systems.,Theory,Medium</t>
-  </si>
-  <si>
-    <t>11,What is ReAct (Reason + Act) pattern in Agentic AI? How does it work?,Technical,Hard</t>
-  </si>
-  <si>
-    <t>12,What is the difference between deterministic workflows and dynamic agentic systems?,Theory,Medium</t>
-  </si>
-  <si>
-    <t>13,How do you evaluate RAG systems? Discuss metrics like faithfulness, answer relevance, and context relevance.,Technical,Medium</t>
-  </si>
-  <si>
-    <t>14,What are the challenges in building production-ready RAG systems (latency, cost, accuracy)?,Theory,Medium</t>
-  </si>
-  <si>
-    <t>15,How does agentic AI handle complex multi-step tasks? Provide examples.,Application,Medium</t>
-  </si>
-  <si>
-    <t>16,What is the role of memory in agentic AI (short-term vs long-term memory)?,Technical,Medium</t>
-  </si>
-  <si>
-    <t>17,Compare LangChain, LlamaIndex, and AutoGen for building agentic systems.,Theory,Medium</t>
-  </si>
-  <si>
-    <t>18,What are the security and safety concerns in agentic AI systems?,Theory,Medium</t>
-  </si>
-  <si>
-    <t>19,How do you decide between RAG, workflow, and agentic AI for a given use case?,Application,Medium</t>
-  </si>
-  <si>
-    <t>20,What is the future of agentic AI? Discuss trends and emerging capabilities.,Theory,Medium</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -105,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -325,118 +316,1133 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Query_ID,Query_Name,Operation_Type,Spark_SQL_Code,DataFrame_API,Input_Records,Output_Records,Execution_Time_Sec,Partitions,Shuffle_Read_MB,Shuffle_Write_MB,Memory_MB,Optimization,Use_Case</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>SQL-001,Create_DataFrame,Create,spark.read.json("data.json"),spark.read.json("data.json"),10000000,10000000,12,8,0,0,2048,No,Load JSON data</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>SQL-002,Create_DataFrame_CSV,Create,spark.read.csv("data.csv", header=True),spark.read.csv("data.csv", header=True),10000000,10000000,15,8,0,0,2048,No,Load CSV data</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>SQL-003,Create_DataFrame_Parquet,Create,spark.read.parquet("data.parquet"),spark.read.parquet("data.parquet"),10000000,10000000,8,8,0,0,2048,No,Load Parquet data</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SQL-004,Show_Data,Action,df.show(10),df.show(10),10000000,10,2,8,0,0,512,No,Preview data</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>SQL-005,Print_Schema,Action,df.printSchema(),df.printSchema(),10000000,0,1,8,0,0,256,No,View schema</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SQL-006,Select_Columns,Transformation,"SELECT name, age FROM df",df.select("name", "age"),10000000,10000000,8,8,0,0,1024,PredicatePushdown,Column projection</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>SQL-007,Filter_Rows,Transformation,"SELECT * FROM df WHERE age &gt; 30",df.filter(df.age &gt; 30),10000000,5000000,12,8,0,0,1024,PredicatePushdown,Row filtering</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SQL-008,Where_Clause,Transformation,"SELECT * FROM df WHERE city = 'NYC'",df.where(df.city == "NYC"),10000000,2000000,10,8,0,0,1024,PredicatePushdown,Filter by condition</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SQL-009,Group_By,Transformation,"SELECT city, COUNT(*) FROM df GROUP BY city",df.groupBy("city").count(),10000000,500,18,16,2560,1920,3072,PartialAggregation,Group by aggregation</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SQL-010,Aggregation_Sum,Transformation,"SELECT city, SUM(sales) FROM df GROUP BY city",df.groupBy("city").sum("sales"),10000000,500,22,16,2560,1920,3072,PartialAggregation,Sum aggregation</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>SQL-011,Aggregation_Multiple,Transformation,"SELECT city, AVG(age), MAX(sales), MIN(sales) FROM df GROUP BY city",df.groupBy("city").agg({"age":"avg", "sales":"max", "sales":"min"}),10000000,500,28,16,2560,1920,4096,PartialAggregation,Multiple aggregations</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SQL-012,Order_By,Transformation,"SELECT * FROM df ORDER BY sales DESC",df.orderBy(df.sales.desc()),10000000,10000000,45,32,3840,3840,4096,SortPushdown,Sorting</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>SQL-013,Limit,Action,"SELECT * FROM df LIMIT 100",df.limit(100),10000000,100,3,8,0,0,512,No,Top N rows</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>SQL-014,Join,Transformation,"SELECT * FROM df1 JOIN df2 ON df1.id = df2.id",df1.join(df2, "id"),20000000,15000000,85,64,5120,3840,8192,BroadcastJoin,Combine tables</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SQL-015,Left_Join,Transformation,"SELECT * FROM df1 LEFT JOIN df2 ON df1.id = df2.id",df1.join(df2, "id", "left"),20000000,18000000,92,64,5120,3840,8192,No,Left outer join</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>SQL-016,Union,Transformation,"SELECT * FROM df1 UNION ALL SELECT * FROM df2",df1.union(df2),20000000,20000000,25,16,0,0,3072,No,Combine data</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>SQL-017,Distinct,Transformation,"SELECT DISTINCT city FROM df",df.select("city").distinct(),10000000,500,18,16,1280,960,2048,No,Unique values</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>SQL-018,Window_Function,Transformation,"SELECT name, sales, RANK() OVER (PARTITION BY city ORDER BY sales DESC) as rank FROM df",df.withColumn("rank", rank().over(Window.partitionBy("city").orderBy(df.sales.desc()))),10000000,10000000,68,32,3840,3840,6144,No,Ranking per group</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SQL-019,With_Column,Transformation,"SELECT *, sales * 0.1 as tax FROM df",df.withColumn("tax", df.sales * 0.1),10000000,10000000,12,8,0,0,1024,No,Add calculated column</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>SQL-020,When_Otherwise,Transformation,"SELECT name, CASE WHEN age &lt; 30 THEN 'Young' WHEN age &lt; 60 THEN 'Middle' ELSE 'Senior' END as age_group FROM df",df.withColumn("age_group", when(df.age &lt; 30, "Young").when(df.age &lt; 60, "Middle").otherwise("Senior")),10000000,10000000,15,8,0,0,1024,No,Conditional column</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SQL-021,Create_Temp_View,Create,df.createOrReplaceTempView("temp_table"),df.createOrReplaceTempView("temp_table"),10000000,10000000,1,8,0,0,256,No,Register temporary view</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>SQL-022,SQL_Query,Transformation,spark.sql("SELECT * FROM temp_table WHERE age &gt; 30"),spark.sql("SELECT * FROM temp_table WHERE age &gt; 30"),10000000,5000000,12,8,0,0,1024,PredicatePushdown,SQL interface</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>SQL-023,Complex_SQL,Transformation,"SELECT city, AVG(sales) as avg_sales, COUNT(*) as cnt FROM temp_table WHERE age &gt; 25 GROUP BY city HAVING AVG(sales) &gt; 1000 ORDER BY avg_sales DESC",spark.sql("SELECT city, AVG(sales) as avg_sales, COUNT(*) as cnt FROM temp_table WHERE age &gt; 25 GROUP BY city HAVING AVG(sales) &gt; 1000 ORDER BY avg_sales DESC"),10000000,100,45,32,3840,2560,4096,PredicatePushdown,Complex analytics</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>SQL-024,Cache_Table,Optimization,spark.catalog.cacheTable("temp_table"),spark.catalog.cacheTable("temp_table"),10000000,10000000,3,8,0,0,4096,No,Cache in memory</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>SQL-025,Uncache_Table,Optimization,spark.catalog.uncacheTable("temp_table"),spark.catalog.uncacheTable("temp_table"),10000000,10000000,2,8,0,0,512,No,Remove from cache</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>SQL-026,Explain_Plan,Optimization,df.explain(),df.explain(),10000000,0,1,8,0,0,256,No,View execution plan</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>SQL-027,Coalesce,Optimization,df.coalesce(4),df.coalesce(4),10000000,10000000,8,4,0,0,1024,No,Reduce partitions</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>SQL-028,Repartition,Optimization,df.repartition(16),df.repartition(16),10000000,10000000,18,16,0,1280,2048,No,Increase partitions</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>SQL-029,Write_Parquet,Action,df.write.parquet("output/"),df.write.parquet("output/"),10000000,10000000,45,8,0,0,3072,No,Save to Parquet</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>SQL-030,Write_JSON,Action,df.write.json("output/"),df.write.json("output/"),10000000,10000000,52,8,0,0,3072,No,Save to JSON</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>What is Spark SQL? Explain its architecture and key components using the dataset.</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Operation_Type, Optimization | Spark SQL is Spark's module for structured data processing. Features: DataFrame API, SQL queries, Catalyst optimizer (predicate pushdown, partial aggregation)</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>Spark SQL bridges relational processing with Spark's distributed engine</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>How do you create DataFrames in Spark SQL? List different ways from the dataset.</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Create operations | Methods: spark.read.json(), spark.read.csv(), spark.read.parquet(), spark.read.table(), spark.range(), spark.createDataFrame()</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>DataFrames can be created from various data sources</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>What are the differences between DataFrame API and SQL? Provide examples from dataset.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Compare SQL-006 (SQL) vs DataFrame API | SQL: spark.sql(SELECT name</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>age FROM df"); DataFrame: df.select("name"</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>How do you filter data in Spark SQL? Write code using both DataFrame API and SQL.</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>From SQL-007, SQL-008 | DataFrame: df.filter(df.age &gt; 30) or df.where(df.city == NYC"); SQL: spark.sql("SELECT * FROM df WHERE age &gt; 30")"</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>Filtering supports predicate pushdown for optimization</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>How do you perform aggregations in Spark SQL? Provide examples with groupBy.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>From SQL-009, SQL-010, SQL-011 | DataFrame: df.groupBy(city").count(); df.groupBy("city").sum("sales"); SQL: SELECT city</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>COUNT(*)</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between groupBy and groupByKey in Spark SQL?</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Analyze performance metrics | groupBy (DataFrame) uses Catalyst optimizer (18-28s); groupByKey (RDD) requires manual optimization (45s). DataFrame API is optimized</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>DataFrame aggregations are optimized by Catalyst</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>How do you sort data in Spark SQL? Write code for ascending and descending order.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>From SQL-012 | DataFrame: df.orderBy(df.sales.desc()) or df.sort(sales"</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>ascending=False); SQL: SELECT * FROM df ORDER BY sales DESC"</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>How do you join DataFrames in Spark SQL? List different join types with code.</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>From SQL-014, SQL-015 | Inner: df1.join(df2, id"); Left: df1.join(df2</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>"id"</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>What is Catalyst Optimizer? How does it improve performance?</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Optimization column | Optimizations: Predicate pushdown (filter before join), Partial aggregation (groupBy), Broadcast joins. Reduces execution time 20-40%</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>Catalyst applies rule-based optimizations to query plans</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>What are the different ways to handle missing data in Spark SQL?</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>Common operations | df.na.drop() - remove null rows; df.na.fill(value) - fill nulls; df.na.replace() - replace values; SQL: WHERE column IS NOT NULL</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>Handle missing data before analysis for accurate results</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>How do you create temporary views? Why are they useful?</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>From SQL-021 | df.createOrReplaceTempView(temp_table"). Views allow SQL queries on DataFrames; session-scoped"</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>Views provide SQL interface without persisting data</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>What is predicate pushdown? Provide example from dataset.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>Analyze SQL-006, SQL-007 | Filter condition pushed to data source (age &gt; 30) before reading. Reduces data read by 50-80%</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>Predicate pushdown significantly reduces I/O</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>What is partial aggregation? How does it improve groupBy performance?</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Analyze SQL-009, SQL-010 | Aggregations performed on each partition before shuffle. Reduces shuffle data by 30-50%</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>Partial aggregation minimizes data transfer</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>How do you optimize joins in Spark SQL? Analyze broadcast joins.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>From SQL-014 broadcast hint | Broadcast hint: df1.join(broadcast(df2), id"). For small tables (&lt;10MB)</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>broadcast avoids shuffle"</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>What are window functions? Provide example with rank.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>From SQL-018 | from pyspark.sql.window import Window; df.withColumn(rank"</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>rank().over(Window.partitionBy("city").orderBy(df.sales.desc())))"</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>How do you add calculated columns? Write code for conditional column.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>From SQL-019, SQL-020 | df.withColumn(tax"</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>df.sales * 0.1); df.withColumn("age_group"</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>How do you cache DataFrames? When should you use caching?</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>From SQL-024, SQL-025 | df.cache() or spark.catalog.cacheTable(table"). Use for DataFrames reused multiple times"</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>Caching avoids recomputation; unpersist when done</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>How do you view the execution plan? What information does it provide?</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>From SQL-026 | df.explain() shows logical and physical plans. Shows filters, projections, shuffles, joins</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>Execution plan helps debug and optimize queries</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>How do you repartition DataFrames? Compare coalesce and repartition.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>From SQL-027, SQL-028 | coalesce: reduces partitions without shuffle (8s); repartition: changes partitions with shuffle (18s)</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>Use coalesce to reduce; repartition to increase partitions</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="0" t="n">
         <v>20</v>
       </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Introducing Spark SQL</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create a complete Spark SQL analysis pipeline: read, filter, aggregate, sort, save.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Combine operations | df = spark.read.parquet(data.parquet"); filtered = df.filter(df.age &gt; 30); aggregated = filtered.groupBy("city").agg({"sales":"avg"}); sorted = aggregated.orderBy("avg(sales)"</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>ascending=False); sorted.write.parquet("output/")"</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>